--- a/backtest_runs/20260410_193731/by_symbol/ABOT/ABOT.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/ABOT/ABOT.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-1958.099999999995</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>98041.90000000001</v>
@@ -587,7 +587,7 @@
         <v>-3674.380000000003</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>94367.52</v>
@@ -633,7 +633,7 @@
         <v>-3424</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>90943.52</v>
@@ -679,7 +679,7 @@
         <v>-8211.18</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>82732.34</v>
@@ -771,7 +771,7 @@
         <v>-1570.759999999995</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>85532.53000000001</v>
@@ -817,7 +817,7 @@
         <v>-1175.930000000001</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>84356.60000000001</v>
@@ -863,7 +863,7 @@
         <v>-639.8600000000019</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>83716.74000000001</v>
@@ -1139,7 +1139,7 @@
         <v>-447.2599999999946</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>93649.55000000002</v>
@@ -1185,7 +1185,7 @@
         <v>-1550.430000000001</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>92099.12000000001</v>
@@ -1231,7 +1231,7 @@
         <v>-1556.850000000007</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>90542.27</v>
@@ -1277,7 +1277,7 @@
         <v>-2938.219999999992</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>87604.05000000002</v>
@@ -1415,7 +1415,7 @@
         <v>-1264.739999999993</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>90336.83</v>
@@ -1461,7 +1461,7 @@
         <v>-1076.420000000006</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>89260.41</v>
@@ -1507,7 +1507,7 @@
         <v>-771.4699999999917</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>88488.94</v>
@@ -1645,7 +1645,7 @@
         <v>-1960.239999999993</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>96420.85000000001</v>
